--- a/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -596,7 +596,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>20</v>

--- a/Unity/Assets/Config/Excel/UnitConfig.xlsx
+++ b/Unity/Assets/Config/Excel/UnitConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>#</t>
   </si>
@@ -88,13 +88,159 @@
   </si>
   <si>
     <t>带有强力攻击技能2</t>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>refabName</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>tring</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空法球子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空法球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲锋子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ske</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>leton</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>huoqiu</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>hongfeng</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>f</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>aqiu</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ske</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>leton</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型说明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">        Player = 1,
+        Monster = 2,
+        NPC = 3,
+        Bullet = 4,
+        ParticleEffect = 5,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +252,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -113,13 +260,30 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -148,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -157,6 +321,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,36 +633,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:J9"/>
+  <dimension ref="B2:L11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.77734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="7.88671875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="6.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.77734375" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="16.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="28.77734375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.88671875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.44140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="6.77734375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
@@ -499,25 +675,31 @@
         <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="L3" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
@@ -525,23 +707,27 @@
         <v>4</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="L4" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
@@ -549,14 +735,12 @@
         <v>16</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>16</v>
@@ -564,68 +748,143 @@
       <c r="J5" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" s="1" customFormat="1" ht="79.2" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>178</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="H7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>278</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="8" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="3:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="G9" s="4"/>
+      <c r="L7" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C10" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D10" s="1">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C11" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>